--- a/artfynd/A 9226-2025 artfynd.xlsx
+++ b/artfynd/A 9226-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132053545</v>
       </c>
       <c r="B2" t="n">
-        <v>84099</v>
+        <v>84100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9226-2025 artfynd.xlsx
+++ b/artfynd/A 9226-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132053545</v>
       </c>
       <c r="B2" t="n">
-        <v>84100</v>
+        <v>84105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9226-2025 artfynd.xlsx
+++ b/artfynd/A 9226-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132053545</v>
       </c>
       <c r="B2" t="n">
-        <v>84105</v>
+        <v>84107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9226-2025 artfynd.xlsx
+++ b/artfynd/A 9226-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132053545</v>
       </c>
       <c r="B2" t="n">
-        <v>84146</v>
+        <v>84148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9226-2025 artfynd.xlsx
+++ b/artfynd/A 9226-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132053545</v>
       </c>
       <c r="B2" t="n">
-        <v>84148</v>
+        <v>84150</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9226-2025 artfynd.xlsx
+++ b/artfynd/A 9226-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132053545</v>
       </c>
       <c r="B2" t="n">
-        <v>84150</v>
+        <v>84158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9226-2025 artfynd.xlsx
+++ b/artfynd/A 9226-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132053545</v>
       </c>
       <c r="B2" t="n">
-        <v>84158</v>
+        <v>84159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9226-2025 artfynd.xlsx
+++ b/artfynd/A 9226-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132053545</v>
+        <v>76896574</v>
       </c>
       <c r="B2" t="n">
-        <v>84159</v>
+        <v>96361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1445</v>
+        <v>812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Späd bäckmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Campylophyllum montanum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Lindb.) B.H.Allen</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jonastorp, Jonastorp, Vrm</t>
+          <t>Hjällstad, delpop 1 (HmUE10), Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>396380</v>
+        <v>396296</v>
       </c>
       <c r="R2" t="n">
-        <v>6712712</v>
+        <v>6712692</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +745,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2015-09-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2015-09-21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hjällstad, liten bäck S om. Ny bäck med arten! Gallrad ungskog vid bäcken. Rikligt med lövträd och en del ved.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,19 +766,1499 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Lövrik barrskog vid skogsbäck</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>20 substratenheter # Block</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>Hm1</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av mossor - uppföljning av kända populationer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>97302285</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96361</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>812</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Späd bäckmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Campylophyllum montanum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Lindb.) B.H.Allen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hjällstad, delpop 1 (HmUE10), Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>396302</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6712689</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Bäck i delvis lövrik barrskog.</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>7 substratenheter # Block i bäcken</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Leif Appelgren, Sigrid Bruvoll</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>97566973</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96361</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>812</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Späd bäckmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Campylophyllum montanum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Lindb.) B.H.Allen</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>utan kapsel</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hjällstad, delpop1 (HmUE10B), Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>396367</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6712677</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Nedströms vägen, skog på sediment där bäcken är nedskuren och meandrande. Bara enstaka block.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Lövrik ung barrskog vid liten skogsbäck på flack sedimentmark</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Block, ca 1,3 m, ca 0,2 dm2</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av mossor - uppföljning av kända populationer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>97567344</v>
+      </c>
+      <c r="B5" t="n">
+        <v>96361</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>812</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Späd bäckmossa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Campylophyllum montanum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Lindb.) B.H.Allen</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hjällstad, delpop1 (HmUE10), Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>396302</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6712692</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Lövrik ung barrskog vid liten skogsbäck</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>4 substratenheter # Block</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av mossor - uppföljning av kända populationer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>108273003</v>
+      </c>
+      <c r="B6" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hjällstad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>396392</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6712785</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Uppföljning av tidigare känd lokal. Lokalen bedöms vara vid god status.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Björk, Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>108273012</v>
+      </c>
+      <c r="B7" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hjällstad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>396395</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6712677</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-04-19</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Återfynd vid tidigare känd lokal. Lokalen bedöms vara vid god status.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anton Björk, Agnes Rengren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>115922393</v>
+      </c>
+      <c r="B8" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hagen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>396390</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6712776</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jonas Göransson, Amanda Rudelius, August Oljeqvist, Carl Teg, Svea Nikula, Brian Johnson, Julia Lea Falk, Hannah Falck, Malin Henell, Albin Tengius</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>115927663</v>
+      </c>
+      <c r="B9" t="n">
+        <v>84158</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Jonastorp, Jonastorp, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>396364</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6712677</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-04-13</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ca 10 st fruktkroppar</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Brian Johnson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132053545</v>
+      </c>
+      <c r="B10" t="n">
+        <v>84209</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Jonastorp, Jonastorp, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>396380</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6712712</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Andreas Öster</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Andreas Öster</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>99663855</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96338</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hjällstad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>396302</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6712692</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Lövrik ung barrskog vid liten skogsbäck</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>92499607</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96350</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hjällstad, liten bäck S om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>396296</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6712692</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2015-09-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2015-09-21</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Gallrad ungskog vid bäcken. Rikligt med lövträd och en del ved.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Lövrik barrskog vid skogsbäck</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>92499609</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96350</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Hjällstad, liten bäck S om, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>396333</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6712686</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2015-09-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2015-09-21</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gallrad ungskog vid bäcken. Rikligt med lövträd och en del ved.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Lövrik barrskog vid skogsbäck</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>99663854</v>
+      </c>
+      <c r="B14" t="n">
+        <v>96350</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hjällstad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>396302</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6712692</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Lövrik ung barrskog vid liten skogsbäck</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>99663851</v>
+      </c>
+      <c r="B15" t="n">
+        <v>30288</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>200985</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Blanksvart trämyra</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lasius fuliginosus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Latreille, 1798)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Hjällstad, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>396367</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6712677</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Dalby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-09-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Lövrik ung barrskog vid liten skogsbäck</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9226-2025 artfynd.xlsx
+++ b/artfynd/A 9226-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -806,6 +811,11 @@
           <t>Biogeografisk uppföljning av mossor - uppföljning av kända populationer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76896574</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -925,6 +935,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97302285</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1053,6 +1068,11 @@
           <t>Biogeografisk uppföljning av mossor - uppföljning av kända populationer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97566973</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1172,6 +1192,11 @@
           <t>Biogeografisk uppföljning av mossor - uppföljning av kända populationer</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97567344</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1290,6 +1315,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108273003</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1408,6 +1438,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108273012</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1531,6 +1566,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115922393</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1633,6 +1673,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115927663</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1739,6 +1784,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132053545</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1841,6 +1891,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99663855</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1948,6 +2003,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92499607</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2055,6 +2115,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92499609</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2157,6 +2222,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99663854</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2259,8 +2329,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99663851</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>